--- a/excel/time_processing.xlsx
+++ b/excel/time_processing.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.373</v>
+        <v>1.539</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.251</v>
+        <v>2.687</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.28</v>
+        <v>1.443</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.323</v>
+        <v>1.292</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.291</v>
+        <v>1.315</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.274</v>
+        <v>1.278</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.215</v>
+        <v>1.364</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.349</v>
+        <v>1.333</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.216</v>
+        <v>1.265</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1.171</v>
+        <v>1.321</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.125</v>
+        <v>1.327</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.198</v>
+        <v>2.345</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.205</v>
+        <v>1.533</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.268</v>
+        <v>1.372</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.259</v>
+        <v>1.344</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -1439,7 +1439,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>TỔNG: 18.798 giây</t>
+          <t>TỔNG: 22.758 giây</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>

--- a/excel/time_processing.xlsx
+++ b/excel/time_processing.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.373</v>
+        <v>2.171</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.251</v>
+        <v>1.338</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.28</v>
+        <v>2.589</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.323</v>
+        <v>1.948</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.291</v>
+        <v>1.382</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.274</v>
+        <v>1.312</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.215</v>
+        <v>1.319</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.349</v>
+        <v>1.382</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.216</v>
+        <v>1.351</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1.171</v>
+        <v>1.468</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.125</v>
+        <v>1.42</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.198</v>
+        <v>1.548</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.205</v>
+        <v>2.594</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.268</v>
+        <v>1.426</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.259</v>
+        <v>1.355</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -1439,7 +1439,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>TỔNG: 18.798 giây</t>
+          <t>TỔNG: 24.603 giây</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>

--- a/excel/time_processing.xlsx
+++ b/excel/time_processing.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>2.171</v>
+        <v>1.502</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.338</v>
+        <v>1.34</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>2.589</v>
+        <v>1.28</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.948</v>
+        <v>1.568</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.382</v>
+        <v>1.523</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.312</v>
+        <v>1.461</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.319</v>
+        <v>1.431</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.382</v>
+        <v>1.501</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.351</v>
+        <v>1.4</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1.468</v>
+        <v>1.461</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.42</v>
+        <v>1.455</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.548</v>
+        <v>1.345</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>2.594</v>
+        <v>1.448</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.426</v>
+        <v>1.348</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.355</v>
+        <v>1.516</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -1439,7 +1439,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>TỔNG: 24.603 giây</t>
+          <t>TỔNG: 21.579 giây</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>

--- a/excel/time_processing.xlsx
+++ b/excel/time_processing.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.502</v>
+        <v>1.562</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.34</v>
+        <v>1.315</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.28</v>
+        <v>1.267</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.568</v>
+        <v>1.193</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.523</v>
+        <v>1.21</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.461</v>
+        <v>1.219</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.431</v>
+        <v>1.17</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.501</v>
+        <v>1.2</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.4</v>
+        <v>1.165</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1.461</v>
+        <v>1.167</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.455</v>
+        <v>1.134</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.345</v>
+        <v>1.242</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.448</v>
+        <v>1.195</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.348</v>
+        <v>1.304</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.516</v>
+        <v>1.329</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
@@ -1439,7 +1439,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>TỔNG: 21.579 giây</t>
+          <t>TỔNG: 18.672 giây</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>

--- a/excel/time_processing.xlsx
+++ b/excel/time_processing.xlsx
@@ -162,7 +162,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -212,7 +212,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -262,7 +262,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -312,7 +312,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -362,7 +362,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -412,7 +412,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -462,7 +462,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -512,7 +512,7 @@
       <row>8</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -562,7 +562,7 @@
       <row>9</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -612,7 +612,7 @@
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="20" name="Image 20" descr="Picture"/>
@@ -662,7 +662,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="22" name="Image 22" descr="Picture"/>
@@ -712,7 +712,7 @@
       <row>12</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="24" name="Image 24" descr="Picture"/>
@@ -762,7 +762,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="26" name="Image 26" descr="Picture"/>
@@ -812,7 +812,7 @@
       <row>14</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="28" name="Image 28" descr="Picture"/>
@@ -862,7 +862,7 @@
       <row>15</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="952500" cy="952500"/>
+    <ext cx="952500" cy="714375"/>
     <pic>
       <nvPicPr>
         <cNvPr id="30" name="Image 30" descr="Picture"/>
@@ -870,6 +870,206 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="714375" cy="952500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="504825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="952500" cy="714375"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1172,7 +1372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1217,11 +1417,11 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>1.562</v>
+        <v>1.766</v>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>575</v>
+        <v>469</v>
       </c>
     </row>
     <row r="3" ht="85" customHeight="1">
@@ -1232,11 +1432,11 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1.315</v>
+        <v>1.29</v>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>696</v>
+        <v>562</v>
       </c>
     </row>
     <row r="4" ht="85" customHeight="1">
@@ -1247,11 +1447,11 @@
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
-        <v>1.267</v>
+        <v>1.319</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>544</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" ht="85" customHeight="1">
@@ -1262,11 +1462,11 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1.193</v>
+        <v>1.263</v>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>420</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" ht="85" customHeight="1">
@@ -1277,11 +1477,11 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1.21</v>
+        <v>1.209</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>737</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7" ht="85" customHeight="1">
@@ -1292,11 +1492,11 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1.219</v>
+        <v>1.152</v>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>910</v>
+        <v>695</v>
       </c>
     </row>
     <row r="8" ht="85" customHeight="1">
@@ -1307,11 +1507,11 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>707</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" ht="85" customHeight="1">
@@ -1322,11 +1522,11 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>1.2</v>
+        <v>1.185</v>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="n">
-        <v>1233</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" ht="85" customHeight="1">
@@ -1337,11 +1537,11 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1.165</v>
+        <v>1.121</v>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>819</v>
+        <v>530</v>
       </c>
     </row>
     <row r="11" ht="85" customHeight="1">
@@ -1352,11 +1552,11 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1.167</v>
+        <v>1.171</v>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>752</v>
+        <v>557</v>
       </c>
     </row>
     <row r="12" ht="85" customHeight="1">
@@ -1367,11 +1567,11 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1.134</v>
+        <v>1.167</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>518</v>
+        <v>449</v>
       </c>
     </row>
     <row r="13" ht="85" customHeight="1">
@@ -1382,11 +1582,11 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1.242</v>
+        <v>1.176</v>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>581</v>
+        <v>418</v>
       </c>
     </row>
     <row r="14" ht="85" customHeight="1">
@@ -1397,11 +1597,11 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>1.195</v>
+        <v>1.184</v>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="n">
-        <v>656</v>
+        <v>525</v>
       </c>
     </row>
     <row r="15" ht="85" customHeight="1">
@@ -1412,11 +1612,11 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.304</v>
+        <v>1.23</v>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>995</v>
       </c>
     </row>
     <row r="16" ht="85" customHeight="1">
@@ -1427,23 +1627,83 @@
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>1.329</v>
+        <v>1.326</v>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="17" ht="85" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A hien.jpg</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>TỔNG: 18.672 giây</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1.92</v>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="n">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="18" ht="85" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>a_ducanh.jpg</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>2.886</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="n">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="19" ht="85" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>For_An.png</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>1.606</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="n">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="20" ht="85" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Phong.jpg</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>1.576</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>TỔNG: 26.707 giây</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
